--- a/chennai_ward_gap_pt_index.xlsx
+++ b/chennai_ward_gap_pt_index.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFE566"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -87,6 +91,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR201"/>
+  <dimension ref="A1:AX201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -502,224 +510,254 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ward_label</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>unit_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>gap_index</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>gap_band</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>pt_index</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>priority_score</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>area_km2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>stop_count</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>shelter_count</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>hub_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>mrts_station_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>cmrl_hub_count</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>railway_station_count</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>has_mrts</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>has_cmrl</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>has_railway</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>has_any_rail_metro</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>nearest_mrts_m</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>nearest_cmrl_m</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="6" t="inlineStr">
         <is>
           <t>nearest_railway_m</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="6" t="inlineStr">
         <is>
           <t>stops_per_km2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>stop_gap</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>shelter_gap</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>hub_gap</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>density_gap</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="6" t="inlineStr">
         <is>
           <t>has_slum</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="6" t="inlineStr">
         <is>
           <t>pct_slum_area</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="6" t="inlineStr">
         <is>
           <t>slum_band</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="6" t="inlineStr">
         <is>
           <t>amenity_deprivation</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="6" t="inlineStr">
         <is>
           <t>amenity_band</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="6" t="inlineStr">
         <is>
           <t>amenity_join</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="6" t="inlineStr">
         <is>
           <t>establishments</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" s="6" t="inlineStr">
         <is>
           <t>total_workers</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" s="6" t="inlineStr">
         <is>
           <t>workers_per_est</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" s="6" t="inlineStr">
         <is>
           <t>population_2011</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" s="6" t="inlineStr">
         <is>
           <t>pop_join_status</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" s="6" t="inlineStr">
         <is>
           <t>pct_area_within_400m</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="6" t="inlineStr">
         <is>
           <t>pct_area_within_800m</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" s="6" t="inlineStr">
         <is>
           <t>pct_area_outside_400m</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" s="6" t="inlineStr">
         <is>
           <t>est_pop_within_400m</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" s="6" t="inlineStr">
         <is>
           <t>coverage_band</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" s="6" t="inlineStr">
         <is>
           <t>shelter_to_stop_ratio</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" s="6" t="inlineStr">
         <is>
           <t>shelter_mismatch_score</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" s="6" t="inlineStr">
         <is>
           <t>top_recommendation</t>
+        </is>
+      </c>
+      <c r="AS1" s="7" t="inlineStr">
+        <is>
+          <t>mean_walk_m</t>
+        </is>
+      </c>
+      <c r="AT1" s="7" t="inlineStr">
+        <is>
+          <t>median_walk_m</t>
+        </is>
+      </c>
+      <c r="AU1" s="7" t="inlineStr">
+        <is>
+          <t>p90_walk_m</t>
+        </is>
+      </c>
+      <c r="AV1" s="7" t="inlineStr">
+        <is>
+          <t>pct_samples_within_400m</t>
+        </is>
+      </c>
+      <c r="AW1" s="7" t="inlineStr">
+        <is>
+          <t>pct_samples_within_800m</t>
+        </is>
+      </c>
+      <c r="AX1" s="7" t="inlineStr">
+        <is>
+          <t>walk_sample_points</t>
         </is>
       </c>
     </row>
@@ -870,6 +908,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS2" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>299.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>653.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1022,6 +1078,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS3" t="n">
+        <v>303.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>645.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1174,6 +1248,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS4" t="n">
+        <v>310.3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>622.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1326,6 +1418,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS5" t="n">
+        <v>278</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>253.9</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>493.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>99</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1478,6 +1588,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS6" t="n">
+        <v>206</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>338</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1626,6 +1754,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS7" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>389.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>608.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1778,6 +1924,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS8" t="n">
+        <v>518.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>479.3</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>916.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>359</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1926,6 +2090,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS9" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>189</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>305.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2078,6 +2260,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS10" t="n">
+        <v>226.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>445.1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2230,6 +2430,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS11" t="n">
+        <v>230.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2382,6 +2600,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS12" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>318.7</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2534,6 +2770,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS13" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2682,6 +2936,24 @@
           <t>No GTFS stops inside boundary</t>
         </is>
       </c>
+      <c r="AS14" t="n">
+        <v>426.3</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>615.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2830,6 +3102,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS15" t="n">
+        <v>201.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>193.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2978,6 +3268,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS16" t="n">
+        <v>1150.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1145</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2032.9</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3130,6 +3438,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS17" t="n">
+        <v>794.9</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>768.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1450.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3282,6 +3608,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS18" t="n">
+        <v>477.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>450.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>833.3</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>318</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3434,6 +3778,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS19" t="n">
+        <v>406.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>689</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>375</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3586,6 +3948,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS20" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>694.1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3738,6 +4118,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS21" t="n">
+        <v>188</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3890,6 +4288,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS22" t="n">
+        <v>533.1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>482.1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>935</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4042,6 +4458,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS23" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>815.7</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4190,6 +4624,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS24" t="n">
+        <v>501.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>486.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>797.7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4338,6 +4790,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS25" t="n">
+        <v>490.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>976.7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>79</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4490,6 +4960,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS26" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>277.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>688.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>188</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4642,6 +5130,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS27" t="n">
+        <v>319.7</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>515.3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4794,6 +5300,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS28" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>322.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>519.5</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4942,6 +5466,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS29" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>314.7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5094,6 +5636,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS30" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>389.8</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>605</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5246,6 +5806,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS31" t="n">
+        <v>348</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>662.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5398,6 +5976,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS32" t="n">
+        <v>400.4</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>743.8</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5550,6 +6146,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS33" t="n">
+        <v>355.4</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>559.8</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>237</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -5702,6 +6316,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS34" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>167.8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -5854,6 +6486,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS35" t="n">
+        <v>238.9</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>228</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6006,6 +6656,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS36" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6154,6 +6822,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS37" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>409</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6302,6 +6988,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS38" t="n">
+        <v>464.8</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>896.9</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>51</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>198</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -6450,6 +7154,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS39" t="n">
+        <v>235</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>396</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -6598,6 +7320,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS40" t="n">
+        <v>205.8</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>344</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -6750,6 +7490,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS41" t="n">
+        <v>160.6</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>154</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>246.4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>98</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6902,6 +7660,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS42" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -7050,6 +7826,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS43" t="n">
+        <v>219</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>92</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -7202,6 +7996,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS44" t="n">
+        <v>198.2</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -7350,6 +8162,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS45" t="n">
+        <v>264.3</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>279.7</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>394.9</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -7498,6 +8328,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS46" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>165.1</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>284.7</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -7650,6 +8498,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS47" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>507</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -7802,6 +8668,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS48" t="n">
+        <v>232.4</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -7950,6 +8834,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS49" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -8102,6 +9004,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS50" t="n">
+        <v>157.9</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>241</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -8254,6 +9174,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS51" t="n">
+        <v>452.6</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>433.6</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>802.5</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -8402,6 +9340,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS52" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>280.1</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>402.8</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -8554,6 +9510,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS53" t="n">
+        <v>147.2</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -8702,6 +9676,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS54" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>261.9</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -8854,6 +9846,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS55" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>261.2</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>446.5</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -9006,6 +10016,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS56" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>579.3</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -9154,6 +10182,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS57" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>286.5</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -9306,6 +10352,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS58" t="n">
+        <v>255.7</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>219.6</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -9454,6 +10518,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS59" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>157</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -9602,6 +10684,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS60" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>163.4</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>366.2</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -9754,6 +10854,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS61" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>280.1</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>769.6</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>66</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>91</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>244</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -9902,6 +11020,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS62" t="n">
+        <v>172.8</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>313.8</v>
+      </c>
+      <c r="AV62" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -10050,6 +11186,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS63" t="n">
+        <v>135.8</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>236</v>
+      </c>
+      <c r="AV63" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX63" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -10198,6 +11352,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS64" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -10350,6 +11522,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS65" t="n">
+        <v>252.2</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>399.4</v>
+      </c>
+      <c r="AV65" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="AW65" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX65" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -10502,6 +11692,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS66" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="AV66" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="AW66" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX66" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -10650,6 +11858,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS67" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>84</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -10802,6 +12028,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS68" t="n">
+        <v>297.8</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>318.7</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>489.4</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -10950,6 +12194,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS69" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -11098,6 +12360,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS70" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>201.1</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>403.3</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -11246,6 +12526,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS71" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>396.4</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -11398,6 +12696,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS72" t="n">
+        <v>179</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -11550,6 +12866,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS73" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>229</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -11698,6 +13032,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS74" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>179.1</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>343</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -11850,6 +13202,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS75" t="n">
+        <v>229.4</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>399.5</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -11998,6 +13368,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS76" t="n">
+        <v>253.4</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>238.6</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>428</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -12146,6 +13534,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS77" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>170.2</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>303.3</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -12294,6 +13700,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS78" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>254.1</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -12446,6 +13870,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS79" t="n">
+        <v>234.6</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>256.2</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>405.7</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -12598,6 +14040,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS80" t="n">
+        <v>309.2</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>564</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>73</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -12750,6 +14210,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS81" t="n">
+        <v>311.1</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>462.4</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -12902,6 +14380,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS82" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>408.1</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -13054,6 +14550,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS83" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>310.7</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>654</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -13206,6 +14720,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS84" t="n">
+        <v>492.3</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>453.4</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>921.3</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>312</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -13358,6 +14890,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS85" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>434</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -13510,6 +15060,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS86" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>316.7</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>652.4</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>98</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -13662,6 +15230,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS87" t="n">
+        <v>300.7</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>514.5</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>76</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>292</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -13814,6 +15400,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS88" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -13966,6 +15570,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS89" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="AT89" t="n">
+        <v>321.1</v>
+      </c>
+      <c r="AU89" t="n">
+        <v>723</v>
+      </c>
+      <c r="AV89" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AW89" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="AX89" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -14118,6 +15740,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS90" t="n">
+        <v>242.8</v>
+      </c>
+      <c r="AT90" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="AU90" t="n">
+        <v>439</v>
+      </c>
+      <c r="AV90" t="n">
+        <v>83</v>
+      </c>
+      <c r="AW90" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX90" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -14266,6 +15906,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS91" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AT91" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="AU91" t="n">
+        <v>408.9</v>
+      </c>
+      <c r="AV91" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="AW91" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -14414,6 +16072,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS92" t="n">
+        <v>237.8</v>
+      </c>
+      <c r="AT92" t="n">
+        <v>223.4</v>
+      </c>
+      <c r="AU92" t="n">
+        <v>430.6</v>
+      </c>
+      <c r="AV92" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="AW92" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX92" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -14566,6 +16242,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS93" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="AT93" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="AU93" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="AV93" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="AW93" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX93" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -14718,6 +16412,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS94" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="AT94" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="AU94" t="n">
+        <v>370</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX94" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -14870,6 +16582,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS95" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>610.9</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -15018,6 +16748,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS96" t="n">
+        <v>263.2</v>
+      </c>
+      <c r="AT96" t="n">
+        <v>235.2</v>
+      </c>
+      <c r="AU96" t="n">
+        <v>480.7</v>
+      </c>
+      <c r="AV96" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="AW96" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX96" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -15166,6 +16914,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS97" t="n">
+        <v>332</v>
+      </c>
+      <c r="AT97" t="n">
+        <v>324.7</v>
+      </c>
+      <c r="AU97" t="n">
+        <v>554.4</v>
+      </c>
+      <c r="AV97" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="AW97" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX97" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -15318,6 +17084,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS98" t="n">
+        <v>237</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>231.6</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>407.3</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -15466,6 +17250,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS99" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>527.4</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -15618,6 +17420,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS100" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>285.7</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -15766,6 +17586,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS101" t="n">
+        <v>201.4</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>188.8</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>95</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -15918,6 +17756,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS102" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -16066,6 +17922,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS103" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>153.7</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -16214,6 +18088,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS104" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>389.7</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>92</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -16366,6 +18258,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS105" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>204</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>373.5</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -16514,6 +18424,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS106" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="AT106" t="n">
+        <v>236.3</v>
+      </c>
+      <c r="AU106" t="n">
+        <v>401.6</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX106" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -16666,6 +18594,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS107" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>341.2</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>643.1</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -16818,6 +18764,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS108" t="n">
+        <v>259.9</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>457.2</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -16966,6 +18930,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS109" t="n">
+        <v>273.1</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>476.2</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -17118,6 +19100,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS110" t="n">
+        <v>478.4</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>541</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>745.3</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -17266,6 +19266,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS111" t="n">
+        <v>209</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>202.9</v>
+      </c>
+      <c r="AU111" t="n">
+        <v>349.5</v>
+      </c>
+      <c r="AV111" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="AW111" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX111" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -17418,6 +19436,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS112" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>192.2</v>
+      </c>
+      <c r="AU112" t="n">
+        <v>396</v>
+      </c>
+      <c r="AV112" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX112" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -17570,6 +19606,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS113" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>303.2</v>
+      </c>
+      <c r="AU113" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="AV113" t="n">
+        <v>68</v>
+      </c>
+      <c r="AW113" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX113" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -17722,6 +19776,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS114" t="n">
+        <v>147.7</v>
+      </c>
+      <c r="AT114" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="AU114" t="n">
+        <v>255.1</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW114" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX114" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -17874,6 +19946,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS115" t="n">
+        <v>199.2</v>
+      </c>
+      <c r="AT115" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AU115" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="AV115" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="AW115" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -18022,6 +20112,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS116" t="n">
+        <v>176.3</v>
+      </c>
+      <c r="AT116" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="AU116" t="n">
+        <v>284.2</v>
+      </c>
+      <c r="AV116" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW116" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX116" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -18170,6 +20278,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS117" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>275</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -18322,6 +20448,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS118" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>304.4</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -18474,6 +20618,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS119" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>194.3</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -18626,6 +20788,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS120" t="n">
+        <v>173</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>165.1</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>326.1</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -18774,6 +20954,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS121" t="n">
+        <v>171.7</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>163</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -18926,6 +21124,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS122" t="n">
+        <v>134.1</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>217.2</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -19078,6 +21294,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS123" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>344</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>94</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -19226,6 +21460,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS124" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -19374,6 +21626,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS125" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -19522,6 +21792,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS126" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>307.7</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -19674,6 +21962,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS127" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -19826,6 +22132,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS128" t="n">
+        <v>246.2</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>417.1</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -19978,6 +22302,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS129" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -20130,6 +22472,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS130" t="n">
+        <v>255.3</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>252.7</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>420.6</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -20278,6 +22638,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS131" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>181</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>410.6</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -20426,6 +22804,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS132" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>207.6</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>98</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -20574,6 +22970,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS133" t="n">
+        <v>314.7</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>535.9</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -20722,6 +23136,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS134" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>163</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -20870,6 +23302,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS135" t="n">
+        <v>221.4</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>232.3</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -21018,6 +23468,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS136" t="n">
+        <v>140.9</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -21166,6 +23634,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS137" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -21318,6 +23804,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS138" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>96</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -21470,6 +23974,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS139" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -21622,6 +24144,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS140" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -21770,6 +24310,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS141" t="n">
+        <v>204.7</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>335</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -21918,6 +24476,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS142" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -22066,6 +24642,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS143" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -22218,6 +24812,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS144" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>533.3</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -22370,6 +24982,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS145" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>401.4</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -22522,6 +25152,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS146" t="n">
+        <v>280.5</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>529.7</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -22674,6 +25322,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS147" t="n">
+        <v>205.3</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>326</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>98</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -22826,6 +25492,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS148" t="n">
+        <v>273.4</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>271.8</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>450.4</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -22978,6 +25662,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS149" t="n">
+        <v>194.7</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -23130,6 +25832,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS150" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>471.3</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -23282,6 +26002,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS151" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>529.9</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -23434,6 +26172,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS152" t="n">
+        <v>238.7</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>220.7</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>412.4</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -23586,6 +26342,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS153" t="n">
+        <v>283</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>273</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>437.4</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -23734,6 +26508,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS154" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>331.3</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>578.3</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -23886,6 +26678,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS155" t="n">
+        <v>254</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>258</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>418</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -24037,6 +26847,24 @@
         <is>
           <t>Shelter gap relative to stops</t>
         </is>
+      </c>
+      <c r="AS156" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>489.7</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="157">
@@ -24174,6 +27002,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS157" t="n">
+        <v>367</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>588.6</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -24310,6 +27156,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS158" t="n">
+        <v>466.4</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>341.8</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>1019.9</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>55</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -24446,6 +27310,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS159" t="n">
+        <v>521.5</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>973.4</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -24582,6 +27464,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS160" t="n">
+        <v>863.7</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>932.7</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>1403.6</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -24718,6 +27618,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS161" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>223.8</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -24854,6 +27772,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS162" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -24990,6 +27926,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS163" t="n">
+        <v>209.2</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>198.8</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -25126,6 +28080,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS164" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>275.9</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -25262,6 +28234,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS165" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -25398,6 +28388,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS166" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -25530,6 +28538,24 @@
           <t>No GTFS stops inside boundary</t>
         </is>
       </c>
+      <c r="AS167" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>542.6</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -25666,6 +28692,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS168" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -25802,6 +28846,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS169" t="n">
+        <v>221.6</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -25934,6 +28996,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS170" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>585.7</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>179</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -26070,6 +29150,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS171" t="n">
+        <v>228.7</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>399.8</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -26202,6 +29300,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS172" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>258.6</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>529.8</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -26338,6 +29454,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS173" t="n">
+        <v>467</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>395.2</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>932.8</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>396</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -26474,6 +29608,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS174" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -26610,6 +29762,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS175" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>293.4</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>726.1</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -26746,6 +29916,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS176" t="n">
+        <v>199.1</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>183</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -26882,6 +30070,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS177" t="n">
+        <v>260.1</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>472.2</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -27014,6 +30220,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS178" t="n">
+        <v>284.9</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>253</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>492.2</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -27146,6 +30370,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS179" t="n">
+        <v>216.2</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>351</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -27278,6 +30520,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS180" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>379</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>787.3</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -27410,6 +30670,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS181" t="n">
+        <v>419.4</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>383.5</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>825</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -27546,6 +30824,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS182" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>690.6</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -27682,6 +30978,24 @@
           <t>Hub present — strengthen last-mile</t>
         </is>
       </c>
+      <c r="AS183" t="n">
+        <v>325.9</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>300.2</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -27818,6 +31132,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS184" t="n">
+        <v>421.3</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>435.8</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -27950,6 +31282,24 @@
           <t>No GTFS stops inside boundary</t>
         </is>
       </c>
+      <c r="AS185" t="n">
+        <v>707.1</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>681.3</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>1145.4</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -28086,6 +31436,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS186" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>161</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -28222,6 +31590,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS187" t="n">
+        <v>297.7</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>301.3</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>458.1</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -28358,6 +31744,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS188" t="n">
+        <v>261.2</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>250.3</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>447.6</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -28490,6 +31894,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS189" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>447.9</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>743.9</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>43</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -28622,6 +32044,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS190" t="n">
+        <v>646.9</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>609.3</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>1130.6</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -28758,6 +32198,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS191" t="n">
+        <v>676.5</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>568.6</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>1373.6</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -28894,6 +32352,24 @@
           <t>Very low stop inventory</t>
         </is>
       </c>
+      <c r="AS192" t="n">
+        <v>872.1</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>876.5</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>1410.8</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>194</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -29030,6 +32506,24 @@
           <t>Below city average stop count</t>
         </is>
       </c>
+      <c r="AS193" t="n">
+        <v>412</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>403.6</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>674.3</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -29166,6 +32660,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS194" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>649.5</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -29298,6 +32810,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS195" t="n">
+        <v>454.1</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>470.7</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>696.6</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -29434,6 +32964,24 @@
           <t>Low shelter-to-stop ratio</t>
         </is>
       </c>
+      <c r="AS196" t="n">
+        <v>257.8</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>259</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>444.8</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -29566,6 +33114,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS197" t="n">
+        <v>306</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>298.4</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>487</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -29698,6 +33264,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS198" t="n">
+        <v>520.5</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>851.5</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>396</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -29830,6 +33414,24 @@
           <t>No rail/metro hub inside boundary</t>
         </is>
       </c>
+      <c r="AS199" t="n">
+        <v>578</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>547.5</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>987</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>293</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -29966,6 +33568,24 @@
           <t>Shelter gap relative to stops</t>
         </is>
       </c>
+      <c r="AS200" t="n">
+        <v>532.8</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>520</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>894.7</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>381</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -30097,6 +33717,24 @@
         <is>
           <t>No rail/metro hub inside boundary</t>
         </is>
+      </c>
+      <c r="AS201" t="n">
+        <v>600.1</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>577.1</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>954.4</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -31242,7 +34880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -31387,6 +35025,30 @@
         <v>40</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mean_walk_m</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mean crow-flies metres from ~150m grid samples in the ward to nearest GTFS stop or MRTS/metro hub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Limitation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Not network walk time; not population-weighted. Community GTFS may under-count MTC stops.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/chennai_ward_gap_pt_index.xlsx
+++ b/chennai_ward_gap_pt_index.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX201"/>
+  <dimension ref="A1:BE201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -760,6 +760,41 @@
           <t>walk_sample_points</t>
         </is>
       </c>
+      <c r="AY1" s="7" t="inlineStr">
+        <is>
+          <t>mean_network_m</t>
+        </is>
+      </c>
+      <c r="AZ1" s="7" t="inlineStr">
+        <is>
+          <t>mean_walk_min</t>
+        </is>
+      </c>
+      <c r="BA1" s="7" t="inlineStr">
+        <is>
+          <t>median_walk_min</t>
+        </is>
+      </c>
+      <c r="BB1" s="7" t="inlineStr">
+        <is>
+          <t>p90_walk_min</t>
+        </is>
+      </c>
+      <c r="BC1" s="7" t="inlineStr">
+        <is>
+          <t>pct_samples_within_5min</t>
+        </is>
+      </c>
+      <c r="BD1" s="7" t="inlineStr">
+        <is>
+          <t>pct_samples_within_10min</t>
+        </is>
+      </c>
+      <c r="BE1" s="7" t="inlineStr">
+        <is>
+          <t>pct_network_routed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -926,6 +961,27 @@
       <c r="AX2" t="n">
         <v>81</v>
       </c>
+      <c r="AY2" t="n">
+        <v>292.1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1096,6 +1152,27 @@
       <c r="AX3" t="n">
         <v>135</v>
       </c>
+      <c r="AY3" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1266,6 +1343,27 @@
       <c r="AX4" t="n">
         <v>150</v>
       </c>
+      <c r="AY4" t="n">
+        <v>392</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1436,6 +1534,27 @@
       <c r="AX5" t="n">
         <v>97</v>
       </c>
+      <c r="AY5" t="n">
+        <v>362.1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1606,6 +1725,27 @@
       <c r="AX6" t="n">
         <v>108</v>
       </c>
+      <c r="AY6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1772,6 +1912,27 @@
       <c r="AX7" t="n">
         <v>63</v>
       </c>
+      <c r="AY7" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1942,6 +2103,27 @@
       <c r="AX8" t="n">
         <v>359</v>
       </c>
+      <c r="AY8" t="n">
+        <v>725.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2108,6 +2290,27 @@
       <c r="AX9" t="n">
         <v>35</v>
       </c>
+      <c r="AY9" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2278,6 +2481,27 @@
       <c r="AX10" t="n">
         <v>31</v>
       </c>
+      <c r="AY10" t="n">
+        <v>241.1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2448,6 +2672,27 @@
       <c r="AX11" t="n">
         <v>25</v>
       </c>
+      <c r="AY11" t="n">
+        <v>273.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>72</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2618,6 +2863,27 @@
       <c r="AX12" t="n">
         <v>28</v>
       </c>
+      <c r="AY12" t="n">
+        <v>136.7</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2788,6 +3054,27 @@
       <c r="AX13" t="n">
         <v>19</v>
       </c>
+      <c r="AY13" t="n">
+        <v>274</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2954,6 +3241,27 @@
       <c r="AX14" t="n">
         <v>19</v>
       </c>
+      <c r="AY14" t="n">
+        <v>587.3</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3120,6 +3428,27 @@
       <c r="AX15" t="n">
         <v>29</v>
       </c>
+      <c r="AY15" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3286,6 +3615,27 @@
       <c r="AX16" t="n">
         <v>400</v>
       </c>
+      <c r="AY16" t="n">
+        <v>1664.3</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3456,6 +3806,27 @@
       <c r="AX17" t="n">
         <v>400</v>
       </c>
+      <c r="AY17" t="n">
+        <v>939.2</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3626,6 +3997,27 @@
       <c r="AX18" t="n">
         <v>318</v>
       </c>
+      <c r="AY18" t="n">
+        <v>671.7</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3796,6 +4188,27 @@
       <c r="AX19" t="n">
         <v>375</v>
       </c>
+      <c r="AY19" t="n">
+        <v>456.3</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3966,6 +4379,27 @@
       <c r="AX20" t="n">
         <v>195</v>
       </c>
+      <c r="AY20" t="n">
+        <v>522</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4136,6 +4570,27 @@
       <c r="AX21" t="n">
         <v>28</v>
       </c>
+      <c r="AY21" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4306,6 +4761,27 @@
       <c r="AX22" t="n">
         <v>84</v>
       </c>
+      <c r="AY22" t="n">
+        <v>658</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4476,6 +4952,27 @@
       <c r="AX23" t="n">
         <v>98</v>
       </c>
+      <c r="AY23" t="n">
+        <v>663.9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4642,6 +5139,27 @@
       <c r="AX24" t="n">
         <v>196</v>
       </c>
+      <c r="AY24" t="n">
+        <v>785.2</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4808,6 +5326,27 @@
       <c r="AX25" t="n">
         <v>124</v>
       </c>
+      <c r="AY25" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4978,6 +5517,27 @@
       <c r="AX26" t="n">
         <v>188</v>
       </c>
+      <c r="AY26" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5148,6 +5708,27 @@
       <c r="AX27" t="n">
         <v>99</v>
       </c>
+      <c r="AY27" t="n">
+        <v>425.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>97</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5318,6 +5899,27 @@
       <c r="AX28" t="n">
         <v>172</v>
       </c>
+      <c r="AY28" t="n">
+        <v>463.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>89</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5484,6 +6086,27 @@
       <c r="AX29" t="n">
         <v>61</v>
       </c>
+      <c r="AY29" t="n">
+        <v>267.1</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5654,6 +6277,27 @@
       <c r="AX30" t="n">
         <v>106</v>
       </c>
+      <c r="AY30" t="n">
+        <v>529.3</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5824,6 +6468,27 @@
       <c r="AX31" t="n">
         <v>143</v>
       </c>
+      <c r="AY31" t="n">
+        <v>482.9</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5994,6 +6659,27 @@
       <c r="AX32" t="n">
         <v>118</v>
       </c>
+      <c r="AY32" t="n">
+        <v>536.7</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6164,6 +6850,27 @@
       <c r="AX33" t="n">
         <v>237</v>
       </c>
+      <c r="AY33" t="n">
+        <v>458.3</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6334,6 +7041,27 @@
       <c r="AX34" t="n">
         <v>30</v>
       </c>
+      <c r="AY34" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6504,6 +7232,27 @@
       <c r="AX35" t="n">
         <v>118</v>
       </c>
+      <c r="AY35" t="n">
+        <v>305</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6674,6 +7423,27 @@
       <c r="AX36" t="n">
         <v>77</v>
       </c>
+      <c r="AY36" t="n">
+        <v>301.8</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6840,6 +7610,27 @@
       <c r="AX37" t="n">
         <v>65</v>
       </c>
+      <c r="AY37" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7006,6 +7797,27 @@
       <c r="AX38" t="n">
         <v>198</v>
       </c>
+      <c r="AY38" t="n">
+        <v>526.4</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7172,6 +7984,27 @@
       <c r="AX39" t="n">
         <v>83</v>
       </c>
+      <c r="AY39" t="n">
+        <v>255.7</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7338,6 +8171,27 @@
       <c r="AX40" t="n">
         <v>49</v>
       </c>
+      <c r="AY40" t="n">
+        <v>228</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7508,6 +8362,27 @@
       <c r="AX41" t="n">
         <v>51</v>
       </c>
+      <c r="AY41" t="n">
+        <v>204</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7678,6 +8553,27 @@
       <c r="AX42" t="n">
         <v>44</v>
       </c>
+      <c r="AY42" t="n">
+        <v>235</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -7844,6 +8740,27 @@
       <c r="AX43" t="n">
         <v>50</v>
       </c>
+      <c r="AY43" t="n">
+        <v>341.3</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>56</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8014,6 +8931,27 @@
       <c r="AX44" t="n">
         <v>48</v>
       </c>
+      <c r="AY44" t="n">
+        <v>333.9</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8180,6 +9118,27 @@
       <c r="AX45" t="n">
         <v>29</v>
       </c>
+      <c r="AY45" t="n">
+        <v>335</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8346,6 +9305,27 @@
       <c r="AX46" t="n">
         <v>54</v>
       </c>
+      <c r="AY46" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8516,6 +9496,27 @@
       <c r="AX47" t="n">
         <v>66</v>
       </c>
+      <c r="AY47" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8686,6 +9687,27 @@
       <c r="AX48" t="n">
         <v>27</v>
       </c>
+      <c r="AY48" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -8852,6 +9874,27 @@
       <c r="AX49" t="n">
         <v>22</v>
       </c>
+      <c r="AY49" t="n">
+        <v>308</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9022,6 +10065,27 @@
       <c r="AX50" t="n">
         <v>37</v>
       </c>
+      <c r="AY50" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9192,6 +10256,27 @@
       <c r="AX51" t="n">
         <v>71</v>
       </c>
+      <c r="AY51" t="n">
+        <v>427.9</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9358,6 +10443,27 @@
       <c r="AX52" t="n">
         <v>19</v>
       </c>
+      <c r="AY52" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9528,6 +10634,27 @@
       <c r="AX53" t="n">
         <v>48</v>
       </c>
+      <c r="AY53" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9694,6 +10821,27 @@
       <c r="AX54" t="n">
         <v>40</v>
       </c>
+      <c r="AY54" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -9864,6 +11012,27 @@
       <c r="AX55" t="n">
         <v>25</v>
       </c>
+      <c r="AY55" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>64</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10034,6 +11203,27 @@
       <c r="AX56" t="n">
         <v>22</v>
       </c>
+      <c r="AY56" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10200,6 +11390,27 @@
       <c r="AX57" t="n">
         <v>26</v>
       </c>
+      <c r="AY57" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10370,6 +11581,27 @@
       <c r="AX58" t="n">
         <v>43</v>
       </c>
+      <c r="AY58" t="n">
+        <v>291</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10536,6 +11768,27 @@
       <c r="AX59" t="n">
         <v>121</v>
       </c>
+      <c r="AY59" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10702,6 +11955,27 @@
       <c r="AX60" t="n">
         <v>133</v>
       </c>
+      <c r="AY60" t="n">
+        <v>234.7</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -10872,6 +12146,27 @@
       <c r="AX61" t="n">
         <v>244</v>
       </c>
+      <c r="AY61" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="BE61" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11038,6 +12333,27 @@
       <c r="AX62" t="n">
         <v>103</v>
       </c>
+      <c r="AY62" t="n">
+        <v>198.4</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB62" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE62" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11204,6 +12520,27 @@
       <c r="AX63" t="n">
         <v>38</v>
       </c>
+      <c r="AY63" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BA63" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11370,6 +12707,27 @@
       <c r="AX64" t="n">
         <v>44</v>
       </c>
+      <c r="AY64" t="n">
+        <v>234.6</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE64" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11540,6 +12898,27 @@
       <c r="AX65" t="n">
         <v>76</v>
       </c>
+      <c r="AY65" t="n">
+        <v>333.6</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA65" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB65" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE65" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11710,6 +13089,27 @@
       <c r="AX66" t="n">
         <v>84</v>
       </c>
+      <c r="AY66" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="AZ66" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA66" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB66" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE66" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -11876,6 +13276,27 @@
       <c r="AX67" t="n">
         <v>50</v>
       </c>
+      <c r="AY67" t="n">
+        <v>364.1</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>58</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12046,6 +13467,27 @@
       <c r="AX68" t="n">
         <v>44</v>
       </c>
+      <c r="AY68" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12212,6 +13654,27 @@
       <c r="AX69" t="n">
         <v>64</v>
       </c>
+      <c r="AY69" t="n">
+        <v>260.5</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12378,6 +13841,27 @@
       <c r="AX70" t="n">
         <v>46</v>
       </c>
+      <c r="AY70" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12544,6 +14028,27 @@
       <c r="AX71" t="n">
         <v>78</v>
       </c>
+      <c r="AY71" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12714,6 +14219,27 @@
       <c r="AX72" t="n">
         <v>72</v>
       </c>
+      <c r="AY72" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -12884,6 +14410,27 @@
       <c r="AX73" t="n">
         <v>63</v>
       </c>
+      <c r="AY73" t="n">
+        <v>262</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13050,6 +14597,27 @@
       <c r="AX74" t="n">
         <v>46</v>
       </c>
+      <c r="AY74" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>87</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13220,6 +14788,27 @@
       <c r="AX75" t="n">
         <v>45</v>
       </c>
+      <c r="AY75" t="n">
+        <v>359</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13386,6 +14975,27 @@
       <c r="AX76" t="n">
         <v>42</v>
       </c>
+      <c r="AY76" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13552,6 +15162,27 @@
       <c r="AX77" t="n">
         <v>27</v>
       </c>
+      <c r="AY77" t="n">
+        <v>222.1</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13718,6 +15349,27 @@
       <c r="AX78" t="n">
         <v>25</v>
       </c>
+      <c r="AY78" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -13888,6 +15540,27 @@
       <c r="AX79" t="n">
         <v>30</v>
       </c>
+      <c r="AY79" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14058,6 +15731,27 @@
       <c r="AX80" t="n">
         <v>100</v>
       </c>
+      <c r="AY80" t="n">
+        <v>402.6</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>54</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>95</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14228,6 +15922,27 @@
       <c r="AX81" t="n">
         <v>65</v>
       </c>
+      <c r="AY81" t="n">
+        <v>418.4</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14398,6 +16113,27 @@
       <c r="AX82" t="n">
         <v>78</v>
       </c>
+      <c r="AY82" t="n">
+        <v>254.4</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14568,6 +16304,27 @@
       <c r="AX83" t="n">
         <v>182</v>
       </c>
+      <c r="AY83" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14738,6 +16495,27 @@
       <c r="AX84" t="n">
         <v>312</v>
       </c>
+      <c r="AY84" t="n">
+        <v>620</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -14908,6 +16686,27 @@
       <c r="AX85" t="n">
         <v>145</v>
       </c>
+      <c r="AY85" t="n">
+        <v>326.8</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15078,6 +16877,27 @@
       <c r="AX86" t="n">
         <v>203</v>
       </c>
+      <c r="AY86" t="n">
+        <v>408.1</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15248,6 +17068,27 @@
       <c r="AX87" t="n">
         <v>292</v>
       </c>
+      <c r="AY87" t="n">
+        <v>384.8</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -15418,6 +17259,27 @@
       <c r="AX88" t="n">
         <v>44</v>
       </c>
+      <c r="AY88" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -15588,6 +17450,27 @@
       <c r="AX89" t="n">
         <v>107</v>
       </c>
+      <c r="AY89" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="AZ89" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -15758,6 +17641,27 @@
       <c r="AX90" t="n">
         <v>47</v>
       </c>
+      <c r="AY90" t="n">
+        <v>362.6</v>
+      </c>
+      <c r="AZ90" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA90" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB90" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="BE90" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -15924,6 +17828,27 @@
       <c r="AX91" t="n">
         <v>52</v>
       </c>
+      <c r="AY91" t="n">
+        <v>437.6</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -16090,6 +18015,27 @@
       <c r="AX92" t="n">
         <v>56</v>
       </c>
+      <c r="AY92" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="AZ92" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA92" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB92" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="BE92" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -16260,6 +18206,27 @@
       <c r="AX93" t="n">
         <v>45</v>
       </c>
+      <c r="AY93" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="AZ93" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA93" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB93" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE93" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -16430,6 +18397,27 @@
       <c r="AX94" t="n">
         <v>66</v>
       </c>
+      <c r="AY94" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="AZ94" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA94" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB94" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="BE94" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -16600,6 +18588,27 @@
       <c r="AX95" t="n">
         <v>69</v>
       </c>
+      <c r="AY95" t="n">
+        <v>477.5</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -16766,6 +18775,27 @@
       <c r="AX96" t="n">
         <v>108</v>
       </c>
+      <c r="AY96" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="AZ96" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA96" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB96" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>63</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="BE96" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -16932,6 +18962,27 @@
       <c r="AX97" t="n">
         <v>132</v>
       </c>
+      <c r="AY97" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="AZ97" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA97" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB97" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="BE97" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -17102,6 +19153,27 @@
       <c r="AX98" t="n">
         <v>34</v>
       </c>
+      <c r="AY98" t="n">
+        <v>306.9</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB98" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE98" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -17268,6 +19340,27 @@
       <c r="AX99" t="n">
         <v>63</v>
       </c>
+      <c r="AY99" t="n">
+        <v>431.5</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -17438,6 +19531,27 @@
       <c r="AX100" t="n">
         <v>58</v>
       </c>
+      <c r="AY100" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="AZ100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA100" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB100" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE100" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -17604,6 +19718,27 @@
       <c r="AX101" t="n">
         <v>101</v>
       </c>
+      <c r="AY101" t="n">
+        <v>281.5</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB101" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>99</v>
+      </c>
+      <c r="BE101" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -17774,6 +19909,27 @@
       <c r="AX102" t="n">
         <v>67</v>
       </c>
+      <c r="AY102" t="n">
+        <v>305.8</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB102" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE102" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -17940,6 +20096,27 @@
       <c r="AX103" t="n">
         <v>83</v>
       </c>
+      <c r="AY103" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -18106,6 +20283,27 @@
       <c r="AX104" t="n">
         <v>112</v>
       </c>
+      <c r="AY104" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -18276,6 +20474,27 @@
       <c r="AX105" t="n">
         <v>103</v>
       </c>
+      <c r="AY105" t="n">
+        <v>313.3</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA105" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB105" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>99</v>
+      </c>
+      <c r="BE105" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -18442,6 +20661,27 @@
       <c r="AX106" t="n">
         <v>59</v>
       </c>
+      <c r="AY106" t="n">
+        <v>317.8</v>
+      </c>
+      <c r="AZ106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA106" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB106" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE106" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -18612,6 +20852,27 @@
       <c r="AX107" t="n">
         <v>37</v>
       </c>
+      <c r="AY107" t="n">
+        <v>501</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -18782,6 +21043,27 @@
       <c r="AX108" t="n">
         <v>57</v>
       </c>
+      <c r="AY108" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -18948,6 +21230,27 @@
       <c r="AX109" t="n">
         <v>70</v>
       </c>
+      <c r="AY109" t="n">
+        <v>394.3</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -19118,6 +21421,27 @@
       <c r="AX110" t="n">
         <v>46</v>
       </c>
+      <c r="AY110" t="n">
+        <v>617.2</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -19284,6 +21608,27 @@
       <c r="AX111" t="n">
         <v>94</v>
       </c>
+      <c r="AY111" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="AZ111" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA111" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB111" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="BE111" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -19454,6 +21799,27 @@
       <c r="AX112" t="n">
         <v>127</v>
       </c>
+      <c r="AY112" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="AZ112" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA112" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB112" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>74</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE112" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -19624,6 +21990,27 @@
       <c r="AX113" t="n">
         <v>50</v>
       </c>
+      <c r="AY113" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="AZ113" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA113" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB113" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>98</v>
+      </c>
+      <c r="BE113" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -19794,6 +22181,27 @@
       <c r="AX114" t="n">
         <v>78</v>
       </c>
+      <c r="AY114" t="n">
+        <v>236.7</v>
+      </c>
+      <c r="AZ114" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA114" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB114" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>91</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE114" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -19964,6 +22372,27 @@
       <c r="AX115" t="n">
         <v>80</v>
       </c>
+      <c r="AY115" t="n">
+        <v>247.6</v>
+      </c>
+      <c r="AZ115" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA115" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB115" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE115" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -20130,6 +22559,27 @@
       <c r="AX116" t="n">
         <v>39</v>
       </c>
+      <c r="AY116" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="AZ116" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA116" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB116" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE116" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -20296,6 +22746,27 @@
       <c r="AX117" t="n">
         <v>31</v>
       </c>
+      <c r="AY117" t="n">
+        <v>202</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -20466,6 +22937,27 @@
       <c r="AX118" t="n">
         <v>64</v>
       </c>
+      <c r="AY118" t="n">
+        <v>222.8</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -20636,6 +23128,27 @@
       <c r="AX119" t="n">
         <v>89</v>
       </c>
+      <c r="AY119" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -20806,6 +23319,27 @@
       <c r="AX120" t="n">
         <v>68</v>
       </c>
+      <c r="AY120" t="n">
+        <v>235</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -20972,6 +23506,27 @@
       <c r="AX121" t="n">
         <v>23</v>
       </c>
+      <c r="AY121" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>87</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -21142,6 +23697,27 @@
       <c r="AX122" t="n">
         <v>42</v>
       </c>
+      <c r="AY122" t="n">
+        <v>190</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -21312,6 +23888,27 @@
       <c r="AX123" t="n">
         <v>84</v>
       </c>
+      <c r="AY123" t="n">
+        <v>289.1</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -21478,6 +24075,27 @@
       <c r="AX124" t="n">
         <v>104</v>
       </c>
+      <c r="AY124" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -21644,6 +24262,27 @@
       <c r="AX125" t="n">
         <v>48</v>
       </c>
+      <c r="AY125" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -21810,6 +24449,27 @@
       <c r="AX126" t="n">
         <v>57</v>
       </c>
+      <c r="AY126" t="n">
+        <v>243.1</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -21980,6 +24640,27 @@
       <c r="AX127" t="n">
         <v>49</v>
       </c>
+      <c r="AY127" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -22150,6 +24831,27 @@
       <c r="AX128" t="n">
         <v>182</v>
       </c>
+      <c r="AY128" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -22320,6 +25022,27 @@
       <c r="AX129" t="n">
         <v>71</v>
       </c>
+      <c r="AY129" t="n">
+        <v>226.6</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -22490,6 +25213,27 @@
       <c r="AX130" t="n">
         <v>90</v>
       </c>
+      <c r="AY130" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -22656,6 +25400,27 @@
       <c r="AX131" t="n">
         <v>52</v>
       </c>
+      <c r="AY131" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -22822,6 +25587,27 @@
       <c r="AX132" t="n">
         <v>50</v>
       </c>
+      <c r="AY132" t="n">
+        <v>259.4</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>84</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -22988,6 +25774,27 @@
       <c r="AX133" t="n">
         <v>51</v>
       </c>
+      <c r="AY133" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>49</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -23154,6 +25961,27 @@
       <c r="AX134" t="n">
         <v>86</v>
       </c>
+      <c r="AY134" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -23320,6 +26148,27 @@
       <c r="AX135" t="n">
         <v>43</v>
       </c>
+      <c r="AY135" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -23486,6 +26335,27 @@
       <c r="AX136" t="n">
         <v>67</v>
       </c>
+      <c r="AY136" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -23652,6 +26522,27 @@
       <c r="AX137" t="n">
         <v>55</v>
       </c>
+      <c r="AY137" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -23822,6 +26713,27 @@
       <c r="AX138" t="n">
         <v>75</v>
       </c>
+      <c r="AY138" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -23992,6 +26904,27 @@
       <c r="AX139" t="n">
         <v>58</v>
       </c>
+      <c r="AY139" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>81</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -24162,6 +27095,27 @@
       <c r="AX140" t="n">
         <v>34</v>
       </c>
+      <c r="AY140" t="n">
+        <v>235.9</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -24328,6 +27282,27 @@
       <c r="AX141" t="n">
         <v>34</v>
       </c>
+      <c r="AY141" t="n">
+        <v>285.9</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -24494,6 +27469,27 @@
       <c r="AX142" t="n">
         <v>34</v>
       </c>
+      <c r="AY142" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -24660,6 +27656,27 @@
       <c r="AX143" t="n">
         <v>50</v>
       </c>
+      <c r="AY143" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>92</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -24830,6 +27847,27 @@
       <c r="AX144" t="n">
         <v>121</v>
       </c>
+      <c r="AY144" t="n">
+        <v>586.5</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -25000,6 +28038,27 @@
       <c r="AX145" t="n">
         <v>66</v>
       </c>
+      <c r="AY145" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>53</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -25170,6 +28229,27 @@
       <c r="AX146" t="n">
         <v>67</v>
       </c>
+      <c r="AY146" t="n">
+        <v>397.5</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>97</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -25340,6 +28420,27 @@
       <c r="AX147" t="n">
         <v>51</v>
       </c>
+      <c r="AY147" t="n">
+        <v>353.3</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -25510,6 +28611,27 @@
       <c r="AX148" t="n">
         <v>92</v>
       </c>
+      <c r="AY148" t="n">
+        <v>420</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>37</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -25680,6 +28802,27 @@
       <c r="AX149" t="n">
         <v>38</v>
       </c>
+      <c r="AY149" t="n">
+        <v>310.8</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -25850,6 +28993,27 @@
       <c r="AX150" t="n">
         <v>65</v>
       </c>
+      <c r="AY150" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -26020,6 +29184,27 @@
       <c r="AX151" t="n">
         <v>167</v>
       </c>
+      <c r="AY151" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>94</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -26190,6 +29375,27 @@
       <c r="AX152" t="n">
         <v>81</v>
       </c>
+      <c r="AY152" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>63</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -26360,6 +29566,27 @@
       <c r="AX153" t="n">
         <v>75</v>
       </c>
+      <c r="AY153" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -26526,6 +29753,27 @@
       <c r="AX154" t="n">
         <v>104</v>
       </c>
+      <c r="AY154" t="n">
+        <v>449.3</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -26696,6 +29944,27 @@
       <c r="AX155" t="n">
         <v>54</v>
       </c>
+      <c r="AY155" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -26865,6 +30134,27 @@
       </c>
       <c r="AX156" t="n">
         <v>69</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>355.6</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="157">
@@ -27020,6 +30310,27 @@
       <c r="AX157" t="n">
         <v>127</v>
       </c>
+      <c r="AY157" t="n">
+        <v>500.9</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -27174,6 +30485,27 @@
       <c r="AX158" t="n">
         <v>211</v>
       </c>
+      <c r="AY158" t="n">
+        <v>711.3</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -27328,6 +30660,27 @@
       <c r="AX159" t="n">
         <v>93</v>
       </c>
+      <c r="AY159" t="n">
+        <v>703.5</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -27482,6 +30835,27 @@
       <c r="AX160" t="n">
         <v>158</v>
       </c>
+      <c r="AY160" t="n">
+        <v>1977.3</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -27636,6 +31010,27 @@
       <c r="AX161" t="n">
         <v>34</v>
       </c>
+      <c r="AY161" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -27790,6 +31185,27 @@
       <c r="AX162" t="n">
         <v>36</v>
       </c>
+      <c r="AY162" t="n">
+        <v>282.7</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -27944,6 +31360,27 @@
       <c r="AX163" t="n">
         <v>58</v>
       </c>
+      <c r="AY163" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>69</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -28098,6 +31535,27 @@
       <c r="AX164" t="n">
         <v>35</v>
       </c>
+      <c r="AY164" t="n">
+        <v>261.9</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -28252,6 +31710,27 @@
       <c r="AX165" t="n">
         <v>26</v>
       </c>
+      <c r="AY165" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -28406,6 +31885,27 @@
       <c r="AX166" t="n">
         <v>55</v>
       </c>
+      <c r="AY166" t="n">
+        <v>309.7</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -28556,6 +32056,27 @@
       <c r="AX167" t="n">
         <v>58</v>
       </c>
+      <c r="AY167" t="n">
+        <v>518.1</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -28710,6 +32231,27 @@
       <c r="AX168" t="n">
         <v>53</v>
       </c>
+      <c r="AY168" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -28864,6 +32406,27 @@
       <c r="AX169" t="n">
         <v>165</v>
       </c>
+      <c r="AY169" t="n">
+        <v>302.9</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -29014,6 +32577,27 @@
       <c r="AX170" t="n">
         <v>179</v>
       </c>
+      <c r="AY170" t="n">
+        <v>428.4</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -29168,6 +32752,27 @@
       <c r="AX171" t="n">
         <v>129</v>
       </c>
+      <c r="AY171" t="n">
+        <v>298.5</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -29318,6 +32923,27 @@
       <c r="AX172" t="n">
         <v>155</v>
       </c>
+      <c r="AY172" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -29472,6 +33098,27 @@
       <c r="AX173" t="n">
         <v>396</v>
       </c>
+      <c r="AY173" t="n">
+        <v>552.8</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -29626,6 +33273,27 @@
       <c r="AX174" t="n">
         <v>127</v>
       </c>
+      <c r="AY174" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -29780,6 +33448,27 @@
       <c r="AX175" t="n">
         <v>161</v>
       </c>
+      <c r="AY175" t="n">
+        <v>419.9</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -29934,6 +33623,27 @@
       <c r="AX176" t="n">
         <v>63</v>
       </c>
+      <c r="AY176" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>81</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -30088,6 +33798,27 @@
       <c r="AX177" t="n">
         <v>83</v>
       </c>
+      <c r="AY177" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -30238,6 +33969,27 @@
       <c r="AX178" t="n">
         <v>128</v>
       </c>
+      <c r="AY178" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>93</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -30388,6 +34140,27 @@
       <c r="AX179" t="n">
         <v>130</v>
       </c>
+      <c r="AY179" t="n">
+        <v>257.5</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -30538,6 +34311,27 @@
       <c r="AX180" t="n">
         <v>84</v>
       </c>
+      <c r="AY180" t="n">
+        <v>543.8</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>81</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -30688,6 +34482,27 @@
       <c r="AX181" t="n">
         <v>84</v>
       </c>
+      <c r="AY181" t="n">
+        <v>587.7</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -30842,6 +34657,27 @@
       <c r="AX182" t="n">
         <v>75</v>
       </c>
+      <c r="AY182" t="n">
+        <v>556.3</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -30996,6 +34832,27 @@
       <c r="AX183" t="n">
         <v>151</v>
       </c>
+      <c r="AY183" t="n">
+        <v>495.4</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -31150,6 +35007,27 @@
       <c r="AX184" t="n">
         <v>68</v>
       </c>
+      <c r="AY184" t="n">
+        <v>571.9</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -31300,6 +35178,27 @@
       <c r="AX185" t="n">
         <v>144</v>
       </c>
+      <c r="AY185" t="n">
+        <v>1034.4</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -31454,6 +35353,27 @@
       <c r="AX186" t="n">
         <v>46</v>
       </c>
+      <c r="AY186" t="n">
+        <v>260.5</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -31608,6 +35528,27 @@
       <c r="AX187" t="n">
         <v>111</v>
       </c>
+      <c r="AY187" t="n">
+        <v>419.9</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -31762,6 +35703,27 @@
       <c r="AX188" t="n">
         <v>44</v>
       </c>
+      <c r="AY188" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -31912,6 +35874,27 @@
       <c r="AX189" t="n">
         <v>158</v>
       </c>
+      <c r="AY189" t="n">
+        <v>611.5</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -32062,6 +36045,27 @@
       <c r="AX190" t="n">
         <v>400</v>
       </c>
+      <c r="AY190" t="n">
+        <v>1054.8</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -32216,6 +36220,27 @@
       <c r="AX191" t="n">
         <v>148</v>
       </c>
+      <c r="AY191" t="n">
+        <v>953.5</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -32370,6 +36395,27 @@
       <c r="AX192" t="n">
         <v>194</v>
       </c>
+      <c r="AY192" t="n">
+        <v>1191.3</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -32524,6 +36570,27 @@
       <c r="AX193" t="n">
         <v>121</v>
       </c>
+      <c r="AY193" t="n">
+        <v>599.6</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -32678,6 +36745,27 @@
       <c r="AX194" t="n">
         <v>98</v>
       </c>
+      <c r="AY194" t="n">
+        <v>474.2</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -32828,6 +36916,27 @@
       <c r="AX195" t="n">
         <v>211</v>
       </c>
+      <c r="AY195" t="n">
+        <v>703</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -32982,6 +37091,27 @@
       <c r="AX196" t="n">
         <v>117</v>
       </c>
+      <c r="AY196" t="n">
+        <v>423.2</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -33132,6 +37262,27 @@
       <c r="AX197" t="n">
         <v>72</v>
       </c>
+      <c r="AY197" t="n">
+        <v>450.1</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -33282,6 +37433,27 @@
       <c r="AX198" t="n">
         <v>396</v>
       </c>
+      <c r="AY198" t="n">
+        <v>698.1</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -33432,6 +37604,27 @@
       <c r="AX199" t="n">
         <v>293</v>
       </c>
+      <c r="AY199" t="n">
+        <v>712.4</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -33586,6 +37779,27 @@
       <c r="AX200" t="n">
         <v>381</v>
       </c>
+      <c r="AY200" t="n">
+        <v>919.5</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -33735,6 +37949,27 @@
       </c>
       <c r="AX201" t="n">
         <v>353</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>829.7</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -34880,7 +39115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -35049,6 +39284,30 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mean_walk_min</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>OSM pedestrian-network path length to nearest stop/hub ÷ 80 m/min (4.8 km/h). Partial — OSM completeness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mean_walk_m</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Crow-flies comparison (kept).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
